--- a/evergreen_yp/data-collection/modbus_reader/tr/modbus_config/tr_modbus_address.xlsx
+++ b/evergreen_yp/data-collection/modbus_reader/tr/modbus_config/tr_modbus_address.xlsx
@@ -1,226 +1,254 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11102"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/chingjenchen/Dropbox/FEMC/Field Deploy/field-deploy/evergreen_yp/data-collection/modbus_reader/tr/modbus_config/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27329653-2CE8-4E47-A571-4D53EAB24949}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-51200" yWindow="500" windowWidth="51200" windowHeight="28300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Connection Config" sheetId="1" r:id="rId5"/>
-    <sheet state="visible" name="Modbus Address" sheetId="2" r:id="rId6"/>
+    <sheet name="Connection Config" sheetId="1" r:id="rId1"/>
+    <sheet name="Modbus Address" sheetId="2" r:id="rId2"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="54">
   <si>
-    <t xml:space="preserve">Connection Type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Device Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Device Type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Port</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Timeout</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Interval</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Destination</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Destination Location</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">192.168.100.130</t>
-  </si>
-  <si>
-    <t xml:space="preserve">502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">filesystem</t>
-  </si>
-  <si>
-    <t xml:space="preserve">data</t>
-  </si>
-  <si>
-    <t xml:space="preserve">address type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">unit id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">display name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">address name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">function code</t>
-  </si>
-  <si>
-    <t xml:space="preserve">address</t>
-  </si>
-  <si>
-    <t xml:space="preserve">data type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">bit length</t>
-  </si>
-  <si>
-    <t xml:space="preserve">signed type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">endianness</t>
-  </si>
-  <si>
-    <t xml:space="preserve">scale</t>
-  </si>
-  <si>
-    <t xml:space="preserve">decimal places</t>
-  </si>
-  <si>
-    <t xml:space="preserve">offset</t>
-  </si>
-  <si>
-    <t xml:space="preserve">enable bit configuration</t>
-  </si>
-  <si>
-    <t xml:space="preserve">bit configuration</t>
-  </si>
-  <si>
-    <t xml:space="preserve">enable parse configuration</t>
-  </si>
-  <si>
-    <t xml:space="preserve">parse configuration</t>
-  </si>
-  <si>
-    <t xml:space="preserve">is warning variable</t>
-  </si>
-  <si>
-    <t xml:space="preserve">warning level</t>
-  </si>
-  <si>
-    <t xml:space="preserve">start address</t>
-  </si>
-  <si>
-    <t xml:space="preserve">data count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">is heartbeat address</t>
-  </si>
-  <si>
-    <t xml:space="preserve">heartbeat interval</t>
-  </si>
-  <si>
-    <t xml:space="preserve">individual</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1</t>
-  </si>
-  <si>
-    <t xml:space="preserve"/>
-  </si>
-  <si>
-    <t xml:space="preserve">temperature</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Double</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unsigned</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Big Endian</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">false</t>
+    <t>Connection Type</t>
+  </si>
+  <si>
+    <t>Device Name</t>
+  </si>
+  <si>
+    <t>Device Type</t>
+  </si>
+  <si>
+    <t>IP</t>
+  </si>
+  <si>
+    <t>Port</t>
+  </si>
+  <si>
+    <t>Timeout</t>
+  </si>
+  <si>
+    <t>Interval</t>
+  </si>
+  <si>
+    <t>Destination</t>
+  </si>
+  <si>
+    <t>Destination Location</t>
+  </si>
+  <si>
+    <t>TCP</t>
+  </si>
+  <si>
+    <t>TR</t>
+  </si>
+  <si>
+    <t>tr</t>
+  </si>
+  <si>
+    <t>502</t>
+  </si>
+  <si>
+    <t>3000</t>
+  </si>
+  <si>
+    <t>1000</t>
+  </si>
+  <si>
+    <t>filesystem</t>
+  </si>
+  <si>
+    <t>data</t>
+  </si>
+  <si>
+    <t>address type</t>
+  </si>
+  <si>
+    <t>unit id</t>
+  </si>
+  <si>
+    <t>group</t>
+  </si>
+  <si>
+    <t>display name</t>
+  </si>
+  <si>
+    <t>address name</t>
+  </si>
+  <si>
+    <t>function code</t>
+  </si>
+  <si>
+    <t>address</t>
+  </si>
+  <si>
+    <t>data type</t>
+  </si>
+  <si>
+    <t>bit length</t>
+  </si>
+  <si>
+    <t>signed type</t>
+  </si>
+  <si>
+    <t>endianness</t>
+  </si>
+  <si>
+    <t>scale</t>
+  </si>
+  <si>
+    <t>decimal places</t>
+  </si>
+  <si>
+    <t>offset</t>
+  </si>
+  <si>
+    <t>enable bit configuration</t>
+  </si>
+  <si>
+    <t>bit configuration</t>
+  </si>
+  <si>
+    <t>enable parse configuration</t>
+  </si>
+  <si>
+    <t>parse configuration</t>
+  </si>
+  <si>
+    <t>is warning variable</t>
+  </si>
+  <si>
+    <t>warning level</t>
+  </si>
+  <si>
+    <t>start address</t>
+  </si>
+  <si>
+    <t>data count</t>
+  </si>
+  <si>
+    <t>is heartbeat address</t>
+  </si>
+  <si>
+    <t>heartbeat interval</t>
+  </si>
+  <si>
+    <t>individual</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>temperature</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>Double</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>Unsigned</t>
+  </si>
+  <si>
+    <t>Big Endian</t>
+  </si>
+  <si>
+    <t>0.1</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>false</t>
+  </si>
+  <si>
+    <t>192.168.100.140</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
     </font>
-    <font/>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
   </fills>
   <borders count="1">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+  <cellXfs count="4">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -410,69 +438,84 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:I2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
+  <cols>
+    <col min="1" max="1" width="14.33203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.33203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.6640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.6640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="4.33203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.33203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.83203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.83203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.1640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="10" max="16384" width="10.83203125" style="3"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="1" t="s">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="F2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="G2" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="H2" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="I2" s="2" t="s">
         <v>16</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -481,155 +524,156 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:X2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.15"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:24" ht="13" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="X1" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="X1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:24" ht="13" x14ac:dyDescent="0.15">
+      <c r="A2" s="1" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="s">
+      <c r="B2" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="C2" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="D2" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="D2" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="E2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="G2" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="H2" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="G2" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="H2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="J2" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="K2" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="L2" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="M2" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="N2" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="M2" s="1" t="s">
+      <c r="O2" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="P2" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="N2" s="1" t="s">
+      <c r="Q2" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="O2" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="P2" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="Q2" s="1" t="s">
-        <v>53</v>
-      </c>
       <c r="R2" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="S2" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="T2" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="U2" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="U2" s="1" t="s">
-        <v>44</v>
-      </c>
       <c r="V2" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="W2" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="X2" s="1" t="s">
         <v>43</v>
-      </c>
-      <c r="W2" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="X2" s="1" t="s">
-        <v>44</v>
       </c>
     </row>
   </sheetData>
